--- a/data/projects/20261017_马桶贴纸/03_产品详情页/马桶贴_产品资料.xlsx
+++ b/data/projects/20261017_马桶贴纸/03_产品详情页/马桶贴_产品资料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -748,7 +748,6 @@
           <t>TTCA-ToiletSticker</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>Parent</t>
@@ -759,25 +758,11 @@
           <t>SET_NAME</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
         <is>
           <t>China</t>
@@ -793,7 +778,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
           <t>https://detail.1688.com/offer/1039619178499.html</t>
@@ -816,7 +800,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>DECORATIVE PATTERN CHOICES: Select Leaf, Fruit, or Floral artwork within the same variation family. Each option keeps the one roll package and the same dimensions while providing a different visual accent for indoor edges and corners.</t>
+          <t>DECORATIVE STYLE CHOICES: Select Leaf, Fruit, or Floral artwork, or a solid White finish, within the same variation family. Each option keeps one roll per package and the same dimensions for easy comparison before ordering.</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -835,6 +819,211 @@
         </is>
       </c>
       <c r="AN2" t="inlineStr">
+        <is>
+          <t>Create a coordinated finishing detail around everyday kitchen and bathroom areas with this self adhesive decorative PVC seam tape. The strip combines a decorative surface with an acrylic adhesive backing in a compact roll that can be measured and trimmed before placement. It is intended for indoor decorative projects around seams, narrow gaps, edges, and corners where a neat finishing accent is desired.
+Each package contains one roll measuring 59.06 inches long and 1.50 inches wide, with an approximate item weight of 0.11 pound. The useful roll format allows the strip to be cut into shorter sections for several small locations or kept in a longer piece for a continuous edge. Leaf, Fruit, and Floral patterns and a solid White option are separate variations; the dimensions and package count remain the same.
+For placement, first measure the intended section and confirm how the strip should be positioned. Wipe away loose dust and residue, allow the area to dry, and cut the strip to the required length with suitable household scissors. Start at one end, remove the release liner gradually, align the strip, and press along its length. Applying the material in stages can make it easier to follow straight edges and work around corner sections.
+This tape is intended for indoor decorative use around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and comparable finishing areas. Surface condition, texture, moisture, and installation method can affect adhesion, so test a small inconspicuous section when compatibility is uncertain. The package includes the decorative tape roll only; tools, fixtures, and surfaces shown in reference imagery are not included.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>父体：价格、包装、制造商和子体专属属性留空。模板精确值：Product Type=ADHESIVE_TAPES，Item Type Keyword=adhesive-tapes，Variation Theme=SET_NAME。主体 PVC；背胶 Acrylic。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>马桶贴纸</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>马桶贴</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Haul Generic Variation</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Generic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Generic</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ADHESIVE_TAPES</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>adhesive-tapes</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>TTCA-ToiletSticker-Leaf</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>TTCA-ToiletSticker</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Child</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SET_NAME</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Green</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>1 decorative seam tape roll</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.99</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>le_4_oz_price_le_3</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>3.94</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.2205</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>https://detail.1688.com/offer/1039619178499.html</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>https://www.amazon.com/dp/B0FQT9V3TC</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Self Adhesive Decorative PVC Seam Tape Roll for Kitchen Sink Bathroom Toilet, Green, 38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>SIMPLE PEEL AND STICK: The acrylic adhesive backing lets you place the decorative PVC strip without adding separate glue. Measure the intended section, cut the roll to length, remove the release liner, and press it onto a clean, dry indoor surface.</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>DECORATIVE LEAF PATTERN: Green botanical artwork adds a fresh visual accent around indoor seams, edges, and corners. The printed design offers an easy way to coordinate small finishing areas with kitchen or bathroom decor.</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>ONE ROLL SIZING: Each package contains one strip measuring 59.06 inches long and 1.50 inches wide. The roll format keeps the material compact before use and provides a practical amount for several small edge or corner sections.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>INDOOR MULTI AREA USE: Intended for decorative placement around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and similar indoor locations where a patterned finishing strip is desired.</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>MEASURE CUT AND APPLY: Wipe the intended area, allow it to dry, measure the section, and trim the strip before placement. Align one end first, remove the liner gradually, and press along the length to position the tape neatly.</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
         <is>
           <t>Create a coordinated finishing detail around everyday kitchen and bathroom areas with this self adhesive decorative PVC seam tape. The strip combines a printed surface with an acrylic adhesive backing in a compact roll that can be measured and trimmed before placement. It is intended for indoor decorative projects around seams, narrow gaps, edges, and corners where a patterned accent is preferred over a plain strip.
 Each package contains one roll measuring 59.06 inches long and 1.50 inches wide, with an approximate item weight of 0.11 pound. The useful roll format allows the strip to be cut into shorter sections for several small locations or kept in a longer piece for a continuous edge. Leaf, Fruit, and Floral options are organized as separate pattern options so the artwork can be selected while the dimensions and package count remain the same.
@@ -842,209 +1031,219 @@
 This tape is intended for indoor decorative use around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and comparable finishing areas. Surface condition, texture, moisture, and installation method can affect adhesion, so test a small inconspicuous section when compatibility is uncertain. The package includes the decorative tape roll only; tools, fixtures, and surfaces shown in reference imagery are not included.</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>父体：价格、包装、制造商和子体专属属性留空。模板精确值：Product Type=ADHESIVE_TAPES，Item Type Keyword=adhesive-tapes，Variation Theme=SET_NAME。主体 PVC；背胶 Acrylic。</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Set Name：Leaf；款式：树叶（春意盎然）。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>1.496</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.1102</t>
+        </is>
+      </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>马桶贴纸</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>马桶贴</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Haul Generic Variation</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>ADHESIVE_TAPES</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>adhesive-tapes</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>TTCA-ToiletSticker-Leaf</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>TTCA-ToiletSticker-Fruit</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>TTCA-ToiletSticker</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Child</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>SET_NAME</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Green</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Multicolor</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>1 decorative seam tape roll</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>le_4_oz_price_le_3</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>3.94</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>3.94</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>0.2205</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>https://detail.1688.com/offer/1039619178499.html</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0FQT9V3TC</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Self Adhesive Decorative PVC Seam Tape Roll for Kitchen Sink Bathroom Toilet, Green, 38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Self Adhesive Decorative PVC Seam Tape Roll for Kitchen Sink Bathroom Toilet, Multicolor, 38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
         <is>
           <t>SIMPLE PEEL AND STICK: The acrylic adhesive backing lets you place the decorative PVC strip without adding separate glue. Measure the intended section, cut the roll to length, remove the release liner, and press it onto a clean, dry indoor surface.</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>DECORATIVE LEAF PATTERN: Green botanical artwork adds a fresh visual accent around indoor seams, edges, and corners. The printed design offers an easy way to coordinate small finishing areas with kitchen or bathroom decor.</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>DECORATIVE FRUIT PATTERN: Colorful fruit artwork adds a cheerful visual accent around indoor seams, edges, and corners. The printed design offers an easy way to coordinate small finishing areas with lively kitchen or bathroom decor.</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>ONE ROLL SIZING: Each package contains one strip measuring 59.06 inches long and 1.50 inches wide. The roll format keeps the material compact before use and provides a practical amount for several small edge or corner sections.</t>
         </is>
       </c>
-      <c r="AL3" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>INDOOR MULTI AREA USE: Intended for decorative placement around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and similar indoor locations where a patterned finishing strip is desired.</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>MEASURE CUT AND APPLY: Wipe the intended area, allow it to dry, measure the section, and trim the strip before placement. Align one end first, remove the liner gradually, and press along the length to position the tape neatly.</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>Create a coordinated finishing detail around everyday kitchen and bathroom areas with this self adhesive decorative PVC seam tape. The strip combines a printed surface with an acrylic adhesive backing in a compact roll that can be measured and trimmed before placement. It is intended for indoor decorative projects around seams, narrow gaps, edges, and corners where a patterned accent is preferred over a plain strip.
 Each package contains one roll measuring 59.06 inches long and 1.50 inches wide, with an approximate item weight of 0.11 pound. The useful roll format allows the strip to be cut into shorter sections for several small locations or kept in a longer piece for a continuous edge. Leaf, Fruit, and Floral options are organized as separate pattern options so the artwork can be selected while the dimensions and package count remain the same.
@@ -1052,221 +1251,219 @@
 This tape is intended for indoor decorative use around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and comparable finishing areas. Surface condition, texture, moisture, and installation method can affect adhesion, so test a small inconspicuous section when compatibility is uncertain. The package includes the decorative tape roll only; tools, fixtures, and surfaces shown in reference imagery are not included.</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Set Name：Leaf；款式：树叶（春意盎然）。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Set Name：Fruit；款式：水果（水果多汁）。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>1.496</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>0.1102</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>马桶贴纸</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>马桶贴</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Haul Generic Variation</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>ADHESIVE_TAPES</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>adhesive-tapes</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>TTCA-ToiletSticker-Fruit</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>TTCA-ToiletSticker-Floral</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>TTCA-ToiletSticker</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Child</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>SET_NAME</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Multicolor</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>1 decorative seam tape roll</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>le_4_oz_price_le_3</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>3.94</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>3.94</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>0.2205</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>https://detail.1688.com/offer/1039619178499.html</t>
         </is>
       </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0FQT9V3TC</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>Self Adhesive Decorative PVC Seam Tape Roll for Kitchen Sink Bathroom Toilet, Multicolor, 38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AI5" t="inlineStr">
         <is>
           <t>SIMPLE PEEL AND STICK: The acrylic adhesive backing lets you place the decorative PVC strip without adding separate glue. Measure the intended section, cut the roll to length, remove the release liner, and press it onto a clean, dry indoor surface.</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>DECORATIVE FRUIT PATTERN: Colorful fruit artwork adds a cheerful visual accent around indoor seams, edges, and corners. The printed design offers an easy way to coordinate small finishing areas with lively kitchen or bathroom decor.</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>DECORATIVE FLORAL PATTERN: Traditional floral artwork adds an ornate visual accent around indoor seams, edges, and corners. The printed design offers an easy way to coordinate small finishing areas with classic kitchen or bathroom decor.</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>ONE ROLL SIZING: Each package contains one strip measuring 59.06 inches long and 1.50 inches wide. The roll format keeps the material compact before use and provides a practical amount for several small edge or corner sections.</t>
         </is>
       </c>
-      <c r="AL4" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>INDOOR MULTI AREA USE: Intended for decorative placement around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and similar indoor locations where a patterned finishing strip is desired.</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>MEASURE CUT AND APPLY: Wipe the intended area, allow it to dry, measure the section, and trim the strip before placement. Align one end first, remove the liner gradually, and press along the length to position the tape neatly.</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>Create a coordinated finishing detail around everyday kitchen and bathroom areas with this self adhesive decorative PVC seam tape. The strip combines a printed surface with an acrylic adhesive backing in a compact roll that can be measured and trimmed before placement. It is intended for indoor decorative projects around seams, narrow gaps, edges, and corners where a patterned accent is preferred over a plain strip.
 Each package contains one roll measuring 59.06 inches long and 1.50 inches wide, with an approximate item weight of 0.11 pound. The useful roll format allows the strip to be cut into shorter sections for several small locations or kept in a longer piece for a continuous edge. Leaf, Fruit, and Floral options are organized as separate pattern options so the artwork can be selected while the dimensions and package count remain the same.
@@ -1274,245 +1471,242 @@
 This tape is intended for indoor decorative use around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and comparable finishing areas. Surface condition, texture, moisture, and installation method can affect adhesion, so test a small inconspicuous section when compatibility is uncertain. The package includes the decorative tape roll only; tools, fixtures, and surfaces shown in reference imagery are not included.</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Set Name：Fruit；款式：水果（水果多汁）。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Set Name：Floral；款式：花团（国风锦华）。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>1.496</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>0.1102</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>马桶贴纸</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>马桶贴</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Haul Generic Variation</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Generic</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>home</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>ADHESIVE_TAPES</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>adhesive-tapes</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>TTCA-ToiletSticker-Floral</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>TTCA-ToiletSticker-White</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>TTCA-ToiletSticker</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Child</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>SET_NAME</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Multicolor</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1 decorative seam tape roll</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.99</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1.86</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>le_4_oz_price_le_3</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>3.94</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>3.94</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0.79</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>0.2205</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>China</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>https://detail.1688.com/offer/1039619178499.html</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>https://www.amazon.com/dp/B0FQT9V3TC</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Self Adhesive Decorative PVC Seam Tape Roll for Kitchen Sink Bathroom Toilet, Multicolor, 38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Self Adhesive Decorative PVC Seam Tape Roll for Kitchen Sink Bathroom Toilet, White, 38 mm x 1.5 m (1.50 in x 4.92 ft)</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
         <is>
           <t>SIMPLE PEEL AND STICK: The acrylic adhesive backing lets you place the decorative PVC strip without adding separate glue. Measure the intended section, cut the roll to length, remove the release liner, and press it onto a clean, dry indoor surface.</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>DECORATIVE FLORAL PATTERN: Traditional floral artwork adds an ornate visual accent around indoor seams, edges, and corners. The printed design offers an easy way to coordinate small finishing areas with classic kitchen or bathroom decor.</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>SOLID WHITE FINISH: The white surface adds a clean visual accent around indoor seams, edges, and corners. Its neutral appearance coordinates with kitchen or bathroom decor while keeping the same size and one-roll package as the other options.</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>ONE ROLL SIZING: Each package contains one strip measuring 59.06 inches long and 1.50 inches wide. The roll format keeps the material compact before use and provides a practical amount for several small edge or corner sections.</t>
         </is>
       </c>
-      <c r="AL5" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>INDOOR MULTI AREA USE: Intended for decorative placement around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and similar indoor locations where a patterned finishing strip is desired.</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>MEASURE CUT AND APPLY: Wipe the intended area, allow it to dry, measure the section, and trim the strip before placement. Align one end first, remove the liner gradually, and press along the length to position the tape neatly.</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>Create a coordinated finishing detail around everyday kitchen and bathroom areas with this self adhesive decorative PVC seam tape. The strip combines a printed surface with an acrylic adhesive backing in a compact roll that can be measured and trimmed before placement. It is intended for indoor decorative projects around seams, narrow gaps, edges, and corners where a patterned accent is preferred over a plain strip.
-Each package contains one roll measuring 59.06 inches long and 1.50 inches wide, with an approximate item weight of 0.11 pound. The useful roll format allows the strip to be cut into shorter sections for several small locations or kept in a longer piece for a continuous edge. Leaf, Fruit, and Floral options are organized as separate pattern options so the artwork can be selected while the dimensions and package count remain the same.
-For placement, first measure the intended section and confirm how the printed design should face. Wipe away loose dust and residue, allow the area to dry, and cut the strip to the required length with suitable household scissors. Start at one end, remove the release liner gradually, align the strip, and press along its length. Applying the material in stages can make it easier to follow straight edges and work around corner sections.
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>Create a coordinated finishing detail around everyday kitchen and bathroom areas with this self adhesive decorative PVC seam tape. The strip combines a decorative surface with an acrylic adhesive backing in a compact roll that can be measured and trimmed before placement. It is intended for indoor decorative projects around seams, narrow gaps, edges, and corners where a neat finishing accent is desired.
+Each package contains one roll measuring 59.06 inches long and 1.50 inches wide, with an approximate item weight of 0.11 pound. The useful roll format allows the strip to be cut into shorter sections for several small locations or kept in a longer piece for a continuous edge. Leaf, Fruit, and Floral patterns and a solid White option are separate variations; the dimensions and package count remain the same.
+For placement, first measure the intended section and confirm how the strip should be positioned. Wipe away loose dust and residue, allow the area to dry, and cut the strip to the required length with suitable household scissors. Start at one end, remove the release liner gradually, align the strip, and press along its length. Applying the material in stages can make it easier to follow straight edges and work around corner sections.
 This tape is intended for indoor decorative use around kitchen countertop seams, sink edges, bathroom corners, toilet base edges, wall corners, and comparable finishing areas. Surface condition, texture, moisture, and installation method can affect adhesion, so test a small inconspicuous section when compatibility is uncertain. The package includes the decorative tape roll only; tools, fixtures, and surfaces shown in reference imagery are not included.</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Set Name：Floral；款式：花团（国风锦华）。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Set Name：White；款式：纯白。主体 PVC；Adhesive Material=Acrylic；Polymer Base Type=Polyvinyl Chloride PVC；Tape Material=Plastic。</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>1.496</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>0.1102</t>
         </is>
